--- a/台股ETF代碼NEW.xlsx
+++ b/台股ETF代碼NEW.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>富邦琤肭磪囓2</t>
+          <t>富邦恒生國企正2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>富邦琤肭磪齯1</t>
+          <t>富邦恒生國企反1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>富邦琤肭磪</t>
+          <t>富邦恒生國企</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
